--- a/exports/DIVISLAB_full_report.xlsx
+++ b/exports/DIVISLAB_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q66"/>
+  <dimension ref="A1:U66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>2.69</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44580.55208333334</v>
+        <v>44581.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>4479.45</v>
+        <v>4386.75</v>
       </c>
       <c r="I2" t="n">
         <v>4460.947060493259</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.19</v>
+        <v>-2.26</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="M2" t="n">
         <v>0.04</v>
       </c>
       <c r="N2" t="n">
-        <v>1.99</v>
+        <v>2.89</v>
       </c>
       <c r="O2" t="n">
         <v>-0.9399999999999999</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>5.88</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44595.55208333334</v>
+        <v>44596.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>4259</v>
+        <v>4342</v>
       </c>
       <c r="I3" t="n">
         <v>4266.193052110411</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K3" t="n">
-        <v>2.91</v>
+        <v>1.02</v>
       </c>
       <c r="L3" t="n">
         <v>2.49</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>7.36</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44613.55208333334</v>
+        <v>44614.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>4251.75</v>
+        <v>4182.5</v>
       </c>
       <c r="I4" t="n">
         <v>4222.309795170263</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.08</v>
+        <v>-3.67</v>
       </c>
       <c r="L4" t="n">
-        <v>3.98</v>
+        <v>4.7</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>2.39</v>
       </c>
       <c r="N4" t="n">
         <v>2.35</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>6.2</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44620.38541666666</v>
+        <v>44620.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>4200</v>
+        <v>4262</v>
       </c>
       <c r="I5" t="n">
         <v>4234.029688104249</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.42</v>
+        <v>-1.9</v>
       </c>
       <c r="L5" t="n">
-        <v>1.82</v>
+        <v>2.36</v>
       </c>
       <c r="M5" t="n">
         <v>2.92</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>7.59</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44651.55208333334</v>
+        <v>44652.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>4424</v>
+        <v>4341.25</v>
       </c>
       <c r="I6" t="n">
         <v>4368.666831543917</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>31</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>1.86</v>
       </c>
       <c r="L6" t="n">
         <v>6.76</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>6.73</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44735.38541666666</v>
+        <v>44735.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>3648.5</v>
+        <v>3665.9</v>
       </c>
       <c r="I7" t="n">
         <v>3649.282327387129</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>83</v>
+        <v>83.16666666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>15.96</v>
+        <v>15.56</v>
       </c>
       <c r="L7" t="n">
         <v>6.9</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>4.64</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44784.55208333334</v>
+        <v>44785.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>3954</v>
+        <v>3770.3</v>
       </c>
       <c r="I8" t="n">
         <v>3797.812993979106</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>49</v>
+        <v>49.83333333333334</v>
       </c>
       <c r="K8" t="n">
-        <v>7.86</v>
+        <v>2.85</v>
       </c>
       <c r="L8" t="n">
         <v>3.27</v>
@@ -897,7 +992,7 @@
         <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.87</v>
+        <v>5.86</v>
       </c>
       <c r="O8" t="n">
         <v>1.41</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>7.35</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44813.55208333334</v>
+        <v>44816.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>3596.65</v>
+        <v>3672.25</v>
       </c>
       <c r="I9" t="n">
         <v>3648.930394385789</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K9" t="n">
-        <v>4.61</v>
+        <v>2.6</v>
       </c>
       <c r="L9" t="n">
         <v>4.98</v>
@@ -954,7 +1061,7 @@
         <v>1.82</v>
       </c>
       <c r="N9" t="n">
-        <v>1.66</v>
+        <v>2.29</v>
       </c>
       <c r="O9" t="n">
         <v>-5.86</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>4.27</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44844.55208333334</v>
+        <v>44845.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>3685</v>
+        <v>3541.6</v>
       </c>
       <c r="I10" t="n">
         <v>3593.635271576967</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K10" t="n">
-        <v>0.35</v>
+        <v>-3.56</v>
       </c>
       <c r="L10" t="n">
-        <v>3.49</v>
+        <v>3.76</v>
       </c>
       <c r="M10" t="n">
         <v>1.45</v>
       </c>
       <c r="N10" t="n">
-        <v>1.46</v>
+        <v>5.01</v>
       </c>
       <c r="O10" t="n">
         <v>2.29</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>7.8</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44865.55208333334</v>
+        <v>44866.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>3607.2</v>
+        <v>3793.1</v>
       </c>
       <c r="I11" t="n">
         <v>3694.128861494989</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.85</v>
+        <v>-7.1</v>
       </c>
       <c r="L11" t="n">
-        <v>4.62</v>
+        <v>7.72</v>
       </c>
       <c r="M11" t="n">
         <v>1.87</v>
       </c>
       <c r="N11" t="n">
-        <v>1.71</v>
+        <v>6.15</v>
       </c>
       <c r="O11" t="n">
         <v>-5.01</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>7.11</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44869.55208333334</v>
+        <v>44872.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>3743</v>
+        <v>3481.95</v>
       </c>
       <c r="I12" t="n">
         <v>3655.40723447274</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.32</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>4.66</v>
+        <v>8.58</v>
       </c>
       <c r="M12" t="n">
         <v>0.04</v>
       </c>
       <c r="N12" t="n">
-        <v>1.11</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="O12" t="n">
         <v>6.15</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>11.28</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44895.55208333334</v>
+        <v>44896.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>3405</v>
+        <v>3421.45</v>
       </c>
       <c r="I13" t="n">
         <v>3406.710969295919</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K13" t="n">
-        <v>2.21</v>
+        <v>1.74</v>
       </c>
       <c r="L13" t="n">
         <v>8.31</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>3.61</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44903.38541666666</v>
+        <v>44903.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>3304.95</v>
+        <v>3287</v>
       </c>
       <c r="I14" t="n">
         <v>3299.5344779694</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.4</v>
+        <v>-3.93</v>
       </c>
       <c r="L14" t="n">
-        <v>3.49</v>
+        <v>3.99</v>
       </c>
       <c r="M14" t="n">
         <v>0.19</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,25 +1454,25 @@
         <v>3.26</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44908.55208333334</v>
+        <v>44909.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>3351.6</v>
+        <v>3372.1</v>
       </c>
       <c r="I15" t="n">
         <v>3366.361465289577</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.97</v>
+        <v>-2.59</v>
       </c>
       <c r="L15" t="n">
-        <v>2.37</v>
+        <v>2.98</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="N15" t="n">
         <v>1.87</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>3.07</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44925.55208333334</v>
+        <v>44928.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>3424</v>
+        <v>3381.05</v>
       </c>
       <c r="I16" t="n">
         <v>3381.152338037882</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K16" t="n">
-        <v>1.54</v>
+        <v>0.27</v>
       </c>
       <c r="L16" t="n">
         <v>2.04</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.24</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45019.38541666666</v>
+        <v>45019.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>2847.25</v>
+        <v>2880</v>
       </c>
       <c r="I17" t="n">
         <v>2862.716292468047</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>91</v>
+        <v>91.16666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>15.79</v>
+        <v>14.82</v>
       </c>
       <c r="L17" t="n">
         <v>4.11</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>4.28</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45062.55208333334</v>
+        <v>45063.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>3276</v>
+        <v>3269.85</v>
       </c>
       <c r="I18" t="n">
         <v>3270.891904260984</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>43</v>
+        <v>43.83333333333334</v>
       </c>
       <c r="K18" t="n">
-        <v>13.75</v>
+        <v>13.54</v>
       </c>
       <c r="L18" t="n">
         <v>1.56</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>5.31</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45068.55208333334</v>
+        <v>45069.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>3255</v>
+        <v>3403.5</v>
       </c>
       <c r="I19" t="n">
         <v>3268.324330851925</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K19" t="n">
-        <v>0.45</v>
+        <v>-4.09</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8100000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="M19" t="n">
         <v>0.6</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>9.56</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45148.55208333334</v>
+        <v>45149.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>3751</v>
+        <v>3693.2</v>
       </c>
       <c r="I20" t="n">
         <v>3700.655654528003</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>79.16666666666667</v>
+        <v>80</v>
       </c>
       <c r="K20" t="n">
-        <v>10.21</v>
+        <v>8.51</v>
       </c>
       <c r="L20" t="n">
         <v>5.36</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>5.47</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45175.38541666666</v>
+        <v>45175.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>3678.85</v>
+        <v>3706.65</v>
       </c>
       <c r="I21" t="n">
         <v>3695.875315436873</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K21" t="n">
-        <v>0.39</v>
+        <v>-0.36</v>
       </c>
       <c r="L21" t="n">
         <v>1.47</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,25 +1937,25 @@
         <v>3.92</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45202.55208333334</v>
+        <v>45203.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>3728.2</v>
+        <v>3668</v>
       </c>
       <c r="I22" t="n">
         <v>3682.85567272273</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>0.58</v>
+        <v>-1.04</v>
       </c>
       <c r="L22" t="n">
         <v>1.5</v>
       </c>
       <c r="M22" t="n">
-        <v>0.59</v>
+        <v>0.76</v>
       </c>
       <c r="N22" t="n">
         <v>2.07</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>5.19</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45236.38541666666</v>
+        <v>45236.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>3346.15</v>
+        <v>3522.4</v>
       </c>
       <c r="I23" t="n">
         <v>3485.296971213962</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K23" t="n">
-        <v>8.77</v>
+        <v>3.97</v>
       </c>
       <c r="L23" t="n">
         <v>3.57</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>8.18</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45267.55208333334</v>
+        <v>45268.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>3735</v>
+        <v>3671.25</v>
       </c>
       <c r="I24" t="n">
         <v>3681.017416826903</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>31</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>6.04</v>
+        <v>4.23</v>
       </c>
       <c r="L24" t="n">
         <v>5.21</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>4.68</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45282.55208333334</v>
+        <v>45286.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>3699.05</v>
+        <v>3808.75</v>
       </c>
       <c r="I25" t="n">
         <v>3766.908915058115</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.76</v>
+        <v>-3.75</v>
       </c>
       <c r="L25" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="M25" t="n">
         <v>0.72</v>
       </c>
       <c r="N25" t="n">
-        <v>1.67</v>
+        <v>4.43</v>
       </c>
       <c r="O25" t="n">
         <v>-1.47</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>6.33</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45302.55208333334</v>
+        <v>45303.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>3906</v>
+        <v>3877</v>
       </c>
       <c r="I26" t="n">
         <v>3881.968713016481</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K26" t="n">
-        <v>2.55</v>
+        <v>1.79</v>
       </c>
       <c r="L26" t="n">
         <v>3.01</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>5.05</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45329.38541666666</v>
+        <v>45329.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>3715.6</v>
+        <v>3739.9</v>
       </c>
       <c r="I27" t="n">
         <v>3732.751579063588</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K27" t="n">
-        <v>4.16</v>
+        <v>3.54</v>
       </c>
       <c r="L27" t="n">
         <v>1.73</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>4.27</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45345.55208333334</v>
+        <v>45348.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>3640</v>
+        <v>3573.05</v>
       </c>
       <c r="I28" t="n">
         <v>3580.03387196913</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>16</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.67</v>
+        <v>-4.46</v>
       </c>
       <c r="L28" t="n">
-        <v>3.82</v>
+        <v>4.54</v>
       </c>
       <c r="M28" t="n">
         <v>0.27</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>5.55</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45358.55208333334</v>
+        <v>45362.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>3593.9</v>
+        <v>3610.65</v>
       </c>
       <c r="I29" t="n">
         <v>3606.217342201726</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.58</v>
+        <v>-1.05</v>
       </c>
       <c r="L29" t="n">
         <v>2.29</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>3.76</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45364.38541666666</v>
+        <v>45364.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>3527.65</v>
+        <v>3468.5</v>
       </c>
       <c r="I30" t="n">
         <v>3474.787386781448</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>2</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.3</v>
+        <v>-3.94</v>
       </c>
       <c r="L30" t="n">
-        <v>3.23</v>
+        <v>4.32</v>
       </c>
       <c r="M30" t="n">
         <v>0.28</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>5.45</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45379.55208333334</v>
+        <v>45383.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>3437</v>
+        <v>3515.25</v>
       </c>
       <c r="I31" t="n">
         <v>3496.343871391961</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>15</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K31" t="n">
-        <v>0.91</v>
+        <v>-1.35</v>
       </c>
       <c r="L31" t="n">
         <v>1.77</v>
       </c>
       <c r="M31" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="N31" t="n">
-        <v>2.08</v>
+        <v>4.39</v>
       </c>
       <c r="O31" t="n">
         <v>-3.05</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>5.07</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45420.55208333334</v>
+        <v>45421.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>3935</v>
+        <v>3771.1</v>
       </c>
       <c r="I32" t="n">
         <v>3844.213918283008</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K32" t="n">
-        <v>11.94</v>
+        <v>7.28</v>
       </c>
       <c r="L32" t="n">
         <v>1.86</v>
@@ -2265,7 +2648,7 @@
         <v>1.03</v>
       </c>
       <c r="N32" t="n">
-        <v>1.75</v>
+        <v>3.66</v>
       </c>
       <c r="O32" t="n">
         <v>4.39</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>8.31</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45430.38541666666</v>
+        <v>45433.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>3928</v>
+        <v>4005</v>
       </c>
       <c r="I33" t="n">
         <v>3986.512249992914</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K33" t="n">
-        <v>-4.16</v>
+        <v>-6.2</v>
       </c>
       <c r="L33" t="n">
-        <v>5.14</v>
+        <v>6.47</v>
       </c>
       <c r="M33" t="n">
         <v>0.43</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>7.89</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45517.55208333334</v>
+        <v>45518.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>4866</v>
+        <v>4662.2</v>
       </c>
       <c r="I34" t="n">
         <v>4723.560550675531</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>84.16666666666667</v>
+        <v>85</v>
       </c>
       <c r="K34" t="n">
-        <v>21.5</v>
+        <v>16.41</v>
       </c>
       <c r="L34" t="n">
         <v>3.87</v>
@@ -2379,7 +2786,7 @@
         <v>1.69</v>
       </c>
       <c r="N34" t="n">
-        <v>3.09</v>
+        <v>4.11</v>
       </c>
       <c r="O34" t="n">
         <v>2.65</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>118</v>
+        <v>119</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>8.119999999999999</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45525.38541666666</v>
+        <v>45525.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>4883</v>
+        <v>4898</v>
       </c>
       <c r="I35" t="n">
         <v>4885.46687915738</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>-4.74</v>
+        <v>-5.06</v>
       </c>
       <c r="L35" t="n">
         <v>6.46</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>5.31</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45586.55208333334</v>
+        <v>45587.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>5915</v>
+        <v>5860</v>
       </c>
       <c r="I36" t="n">
         <v>5878.793942026286</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>61</v>
+        <v>61.83333333333334</v>
       </c>
       <c r="K36" t="n">
-        <v>20.76</v>
+        <v>19.64</v>
       </c>
       <c r="L36" t="n">
         <v>1.41</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>5.9</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45617.55208333334</v>
+        <v>45618.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>5973.95</v>
+        <v>6018.75</v>
       </c>
       <c r="I37" t="n">
         <v>5999.605292201408</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.94</v>
+        <v>-2.71</v>
       </c>
       <c r="L37" t="n">
         <v>5.03</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>5.2</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45632.55208333334</v>
+        <v>45635.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>6134</v>
+        <v>5973.5</v>
       </c>
       <c r="I38" t="n">
         <v>5998.623581475604</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K38" t="n">
-        <v>1.91</v>
+        <v>-0.75</v>
       </c>
       <c r="L38" t="n">
         <v>2.54</v>
       </c>
       <c r="M38" t="n">
-        <v>1.2</v>
+        <v>2.19</v>
       </c>
       <c r="N38" t="n">
-        <v>2.56</v>
+        <v>2.97</v>
       </c>
       <c r="O38" t="n">
         <v>0.44</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>5.84</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45656.38541666666</v>
+        <v>45656.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>5951.95</v>
+        <v>6030</v>
       </c>
       <c r="I39" t="n">
         <v>6025.629104573914</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K39" t="n">
-        <v>0.36</v>
+        <v>-0.95</v>
       </c>
       <c r="L39" t="n">
-        <v>1.36</v>
+        <v>2.77</v>
       </c>
       <c r="M39" t="n">
         <v>0.63</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>4.68</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45663.38541666666</v>
+        <v>45663.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>5895.3</v>
+        <v>5860.2</v>
       </c>
       <c r="I40" t="n">
         <v>5860.817630672345</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.23</v>
+        <v>-2.82</v>
       </c>
       <c r="L40" t="n">
         <v>3.13</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>5.71</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45689.55208333334</v>
+        <v>45691.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>5625</v>
+        <v>5805.45</v>
       </c>
       <c r="I41" t="n">
         <v>5792.178382131755</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>26</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K41" t="n">
-        <v>4.01</v>
+        <v>0.93</v>
       </c>
       <c r="L41" t="n">
         <v>3.55</v>
@@ -2778,7 +3269,7 @@
         <v>1.2</v>
       </c>
       <c r="N41" t="n">
-        <v>4.51</v>
+        <v>5.78</v>
       </c>
       <c r="O41" t="n">
         <v>-3.01</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>10</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45708.55208333334</v>
+        <v>45709.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>5987.95</v>
+        <v>5786.3</v>
       </c>
       <c r="I42" t="n">
         <v>5789.004462605159</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K42" t="n">
-        <v>3.14</v>
+        <v>-0.33</v>
       </c>
       <c r="L42" t="n">
         <v>5.76</v>
@@ -2835,7 +3338,7 @@
         <v>0.51</v>
       </c>
       <c r="N42" t="n">
-        <v>3.23</v>
+        <v>4.76</v>
       </c>
       <c r="O42" t="n">
         <v>5.78</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>8.02</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45734.55208333334</v>
+        <v>45735.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>5783</v>
+        <v>5821</v>
       </c>
       <c r="I43" t="n">
         <v>5793.469326958503</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K43" t="n">
-        <v>0.06</v>
+        <v>-0.6</v>
       </c>
       <c r="L43" t="n">
         <v>3.66</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>5.52</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45744.55208333334</v>
+        <v>45748.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>5738</v>
+        <v>5562.1</v>
       </c>
       <c r="I44" t="n">
         <v>5631.561260181621</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>13</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.43</v>
+        <v>-4.45</v>
       </c>
       <c r="L44" t="n">
-        <v>1.61</v>
+        <v>4.48</v>
       </c>
       <c r="M44" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="N44" t="n">
-        <v>1.64</v>
+        <v>3.36</v>
       </c>
       <c r="O44" t="n">
         <v>0.73</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>8.369999999999999</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45762.38541666666</v>
+        <v>45762.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>5692.5</v>
+        <v>5756</v>
       </c>
       <c r="I45" t="n">
         <v>5713.521245354446</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.34</v>
+        <v>-3.49</v>
       </c>
       <c r="L45" t="n">
         <v>7.33</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.1</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45824.55208333334</v>
+        <v>45825.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>6690</v>
+        <v>6532.5</v>
       </c>
       <c r="I46" t="n">
         <v>6540.644710835596</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>62</v>
+        <v>62.83333333333334</v>
       </c>
       <c r="K46" t="n">
-        <v>16.23</v>
+        <v>13.49</v>
       </c>
       <c r="L46" t="n">
         <v>2.78</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>5.18</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45838.38541666666</v>
+        <v>45838.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>6727.5</v>
+        <v>6828</v>
       </c>
       <c r="I47" t="n">
         <v>6744.584645742932</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K47" t="n">
-        <v>-2.99</v>
+        <v>-4.52</v>
       </c>
       <c r="L47" t="n">
-        <v>3.36</v>
+        <v>4.54</v>
       </c>
       <c r="M47" t="n">
         <v>0.63</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>4.52</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45856.38541666666</v>
+        <v>45856.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>6728</v>
+        <v>6711</v>
       </c>
       <c r="I48" t="n">
         <v>6719.37269500708</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>17.83333333333333</v>
+        <v>18</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.46</v>
+        <v>-1.71</v>
       </c>
       <c r="L48" t="n">
         <v>4.14</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>3.99</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45918.55208333334</v>
+        <v>45919.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>6129</v>
+        <v>6213</v>
       </c>
       <c r="I49" t="n">
         <v>6195.875678507782</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>62</v>
+        <v>62.83333333333334</v>
       </c>
       <c r="K49" t="n">
-        <v>8.67</v>
+        <v>7.42</v>
       </c>
       <c r="L49" t="n">
         <v>0.66</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>3.64</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45924.38541666666</v>
+        <v>45924.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>6049</v>
+        <v>5978</v>
       </c>
       <c r="I50" t="n">
         <v>5987.011982647597</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.64</v>
+        <v>-3.78</v>
       </c>
       <c r="L50" t="n">
-        <v>3.35</v>
+        <v>3.99</v>
       </c>
       <c r="M50" t="n">
         <v>0.02</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>4.17</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45936.55208333334</v>
+        <v>45937.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>5816</v>
+        <v>6050</v>
       </c>
       <c r="I51" t="n">
         <v>5922.937278085832</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>2.71</v>
+        <v>-1.2</v>
       </c>
       <c r="L51" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="M51" t="n">
         <v>0.86</v>
       </c>
       <c r="N51" t="n">
-        <v>2.47</v>
+        <v>5.16</v>
       </c>
       <c r="O51" t="n">
         <v>-1</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>6.53</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45971.55208333334</v>
+        <v>45972.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>6705</v>
+        <v>6503</v>
       </c>
       <c r="I52" t="n">
         <v>6565.76382196534</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K52" t="n">
-        <v>10.83</v>
+        <v>7.49</v>
       </c>
       <c r="L52" t="n">
         <v>3.61</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>7.32</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46010.55208333334</v>
+        <v>46013.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>6460</v>
+        <v>6521.5</v>
       </c>
       <c r="I53" t="n">
         <v>6507.128366841889</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K53" t="n">
-        <v>0.66</v>
+        <v>-0.28</v>
       </c>
       <c r="L53" t="n">
         <v>3.41</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,25 +4145,25 @@
         <v>4.42</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46035.55208333334</v>
+        <v>46036.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>6421.5</v>
+        <v>6373</v>
       </c>
       <c r="I54" t="n">
         <v>6391.397827725811</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.53</v>
+        <v>-2.28</v>
       </c>
       <c r="L54" t="n">
         <v>3.63</v>
       </c>
       <c r="M54" t="n">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
       <c r="N54" t="n">
         <v>2.23</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>5.77</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46064.38541666666</v>
+        <v>46064.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>6241.5</v>
+        <v>6394.5</v>
       </c>
       <c r="I55" t="n">
         <v>6278.682551170558</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K55" t="n">
-        <v>2.06</v>
+        <v>-0.34</v>
       </c>
       <c r="L55" t="n">
-        <v>1.4</v>
+        <v>6.59</v>
       </c>
       <c r="M55" t="n">
         <v>3.04</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.55</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46093.55208333334</v>
+        <v>46094.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>6285.5</v>
+        <v>6104.5</v>
       </c>
       <c r="I56" t="n">
         <v>6165.104215742808</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>29</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.7</v>
+        <v>-4.54</v>
       </c>
       <c r="L56" t="n">
         <v>6.04</v>
@@ -3633,7 +4304,7 @@
         <v>1.94</v>
       </c>
       <c r="N56" t="n">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="O56" t="n">
         <v>3.92</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>7.35</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46125.55208333334</v>
+        <v>46127.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>6068.5</v>
+        <v>6172</v>
       </c>
       <c r="I57" t="n">
         <v>6123.638852619351</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K57" t="n">
-        <v>0.59</v>
+        <v>-1.11</v>
       </c>
       <c r="L57" t="n">
         <v>3.63</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.69</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46171.55208333334</v>
+        <v>46174.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>6682</v>
+        <v>6582.5</v>
       </c>
       <c r="I58" t="n">
         <v>6638.913140651563</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K58" t="n">
-        <v>8.26</v>
+        <v>6.65</v>
       </c>
       <c r="L58" t="n">
         <v>1.15</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>6.1</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46209.38541666666</v>
+        <v>46209.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>6796.5</v>
+        <v>6857.5</v>
       </c>
       <c r="I59" t="n">
         <v>6802.035016316288</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K59" t="n">
-        <v>-3.25</v>
+        <v>-4.18</v>
       </c>
       <c r="L59" t="n">
-        <v>4.63</v>
+        <v>4.67</v>
       </c>
       <c r="M59" t="n">
         <v>0.89</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>4.02</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46280.38541666666</v>
+        <v>46280.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>9236.5</v>
+        <v>9174.5</v>
       </c>
       <c r="I60" t="n">
         <v>9177.905124899222</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>70.83333333333333</v>
+        <v>71</v>
       </c>
       <c r="K60" t="n">
-        <v>34.69</v>
+        <v>33.79</v>
       </c>
       <c r="L60" t="n">
         <v>2.4</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>3.94</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46287.55208333334</v>
+        <v>46288.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>9320.5</v>
+        <v>9498</v>
       </c>
       <c r="I61" t="n">
         <v>9450.059458658687</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.59</v>
+        <v>-3.53</v>
       </c>
       <c r="L61" t="n">
-        <v>3.13</v>
+        <v>3.65</v>
       </c>
       <c r="M61" t="n">
         <v>0.49</v>
       </c>
       <c r="N61" t="n">
-        <v>2.13</v>
+        <v>2.69</v>
       </c>
       <c r="O61" t="n">
         <v>-1.81</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>4.52</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46295.38541666666</v>
+        <v>46295.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>9375.5</v>
+        <v>9279</v>
       </c>
       <c r="I62" t="n">
         <v>9282.638021074968</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.29</v>
+        <v>-2.31</v>
       </c>
       <c r="L62" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="M62" t="n">
         <v>0.32</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>4.49</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46301.55208333334</v>
+        <v>46302.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>9543.5</v>
+        <v>9575.5</v>
       </c>
       <c r="I63" t="n">
         <v>9547.30637202343</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.85</v>
+        <v>-3.2</v>
       </c>
       <c r="L63" t="n">
-        <v>3</v>
+        <v>4.11</v>
       </c>
       <c r="M63" t="n">
         <v>0.55</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>4.57</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46308.55208333334</v>
+        <v>46309.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>9270</v>
+        <v>9027.5</v>
       </c>
       <c r="I64" t="n">
         <v>9174.958246095497</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K64" t="n">
-        <v>-3.19</v>
+        <v>-5.72</v>
       </c>
       <c r="L64" t="n">
-        <v>4.29</v>
+        <v>5.72</v>
       </c>
       <c r="M64" t="n">
         <v>0.45</v>
       </c>
       <c r="N64" t="n">
-        <v>1.74</v>
+        <v>3</v>
       </c>
       <c r="O64" t="n">
         <v>0.16</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>6.68</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46321.55208333334</v>
+        <v>46322.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>9050</v>
+        <v>9442</v>
       </c>
       <c r="I65" t="n">
         <v>9348.420191626194</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.25</v>
+        <v>-4.59</v>
       </c>
       <c r="L65" t="n">
-        <v>3.28</v>
+        <v>4.67</v>
       </c>
       <c r="M65" t="n">
         <v>1.17</v>
       </c>
       <c r="N65" t="n">
-        <v>1.46</v>
+        <v>4.67</v>
       </c>
       <c r="O65" t="n">
         <v>-3</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4206,6 +4997,12 @@
       <c r="Q66" t="n">
         <v>2</v>
       </c>
+      <c r="R66" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6308,7 +7105,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.3</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="6">
@@ -6318,7 +7115,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.6</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="7">
@@ -6328,7 +7125,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="8">
@@ -6338,7 +7135,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="9">
@@ -6348,7 +7145,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31.6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -6358,7 +7155,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>61.7</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="11">
@@ -6368,7 +7165,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
@@ -6378,7 +7175,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -6388,7 +7185,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>68.8</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="14">
@@ -6398,7 +7195,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.03</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="15">
@@ -6408,7 +7205,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.64</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="16">
@@ -6418,7 +7215,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.42</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="17">
@@ -6428,7 +7225,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>34.69</v>
+        <v>33.79</v>
       </c>
     </row>
     <row r="18">
@@ -6438,7 +7235,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>56.2</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="19">
@@ -6448,7 +7245,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.39</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="20">
@@ -6458,7 +7255,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.32</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="21">
@@ -6468,7 +7265,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.31</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="22">
@@ -6478,7 +7275,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -6498,7 +7295,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="25">
@@ -6518,7 +7315,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.58</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="27">
@@ -6528,7 +7325,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.27</v>
+        <v>8.630000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -6538,7 +7335,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
